--- a/docs/proposals/softbank-ultraman-caravan/SB様提示用_エリア別ライン供給計画.xlsx
+++ b/docs/proposals/softbank-ultraman-caravan/SB様提示用_エリア別ライン供給計画.xlsx
@@ -1906,7 +1906,7 @@
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
-          <t>広島・岡山を拠点に各県、沖縄は本島中心</t>
+          <t>広島を拠点に各県、沖縄は本島中心</t>
         </is>
       </c>
       <c r="I10" s="13" t="inlineStr">
@@ -1973,7 +1973,7 @@
     <row r="17">
       <c r="A17" s="19" t="inlineStr">
         <is>
-          <t>・北関東エリアは2027年1〜3月は実施できません(4月以降は可)。</t>
+          <t>・関信越エリア(埼玉・茨城・群馬・栃木・山梨・長野・新潟)は2027年1〜3月は実施できません(4月以降は可)。</t>
         </is>
       </c>
     </row>

--- a/docs/proposals/softbank-ultraman-caravan/SB様提示用_エリア別ライン供給計画.xlsx
+++ b/docs/proposals/softbank-ultraman-caravan/SB様提示用_エリア別ライン供給計画.xlsx
@@ -544,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD13"/>
+  <dimension ref="A1:AA13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -572,17 +572,14 @@
     <col width="6.5" customWidth="1" min="23" max="23"/>
     <col width="6.5" customWidth="1" min="24" max="24"/>
     <col width="6.5" customWidth="1" min="25" max="25"/>
-    <col width="6.5" customWidth="1" min="26" max="26"/>
-    <col width="6.5" customWidth="1" min="27" max="27"/>
-    <col width="6.5" customWidth="1" min="28" max="28"/>
-    <col width="13" customWidth="1" min="29" max="29"/>
-    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>エリア別 月別ライン供給計画(2027年1月〜2029年3月)</t>
+          <t>エリア別 月別ライン供給計画(2027年1月〜2028年12月)</t>
         </is>
       </c>
     </row>
@@ -721,27 +718,12 @@
       </c>
       <c r="Z4" s="4" t="inlineStr">
         <is>
-          <t>2029/1</t>
+          <t>24ヶ月 現場数(基準)</t>
         </is>
       </c>
       <c r="AA4" s="4" t="inlineStr">
         <is>
-          <t>2029/2</t>
-        </is>
-      </c>
-      <c r="AB4" s="4" t="inlineStr">
-        <is>
-          <t>2029/3</t>
-        </is>
-      </c>
-      <c r="AC4" s="4" t="inlineStr">
-        <is>
-          <t>27ヶ月 現場数(基準)</t>
-        </is>
-      </c>
-      <c r="AD4" s="4" t="inlineStr">
-        <is>
-          <t>27ヶ月 現場数(最大)</t>
+          <t>24ヶ月 現場数(最大)</t>
         </is>
       </c>
     </row>
@@ -823,20 +805,11 @@
       <c r="Y5" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="Z5" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA5" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB5" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC5" s="5" t="n">
-        <v>235</v>
-      </c>
-      <c r="AD5" s="5" t="n">
-        <v>235</v>
+      <c r="Z5" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="AA5" s="5" t="n">
+        <v>210</v>
       </c>
     </row>
     <row r="6">
@@ -917,20 +890,11 @@
       <c r="Y6" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="Z6" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA6" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB6" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC6" s="10" t="n">
-        <v>1410</v>
-      </c>
-      <c r="AD6" s="10" t="n">
-        <v>1602</v>
+      <c r="Z6" s="10" t="n">
+        <v>1260</v>
+      </c>
+      <c r="AA6" s="10" t="n">
+        <v>1436</v>
       </c>
     </row>
     <row r="7">
@@ -1011,20 +975,11 @@
       <c r="Y7" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="Z7" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA7" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB7" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC7" s="10" t="n">
-        <v>470</v>
-      </c>
-      <c r="AD7" s="10" t="n">
-        <v>566</v>
+      <c r="Z7" s="10" t="n">
+        <v>420</v>
+      </c>
+      <c r="AA7" s="10" t="n">
+        <v>508</v>
       </c>
     </row>
     <row r="8">
@@ -1105,20 +1060,11 @@
       <c r="Y8" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="Z8" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA8" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB8" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC8" s="10" t="n">
-        <v>470</v>
-      </c>
-      <c r="AD8" s="10" t="n">
-        <v>566</v>
+      <c r="Z8" s="10" t="n">
+        <v>420</v>
+      </c>
+      <c r="AA8" s="10" t="n">
+        <v>508</v>
       </c>
     </row>
     <row r="9">
@@ -1199,20 +1145,11 @@
       <c r="Y9" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="Z9" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA9" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB9" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC9" s="10" t="n">
-        <v>470</v>
-      </c>
-      <c r="AD9" s="10" t="n">
-        <v>566</v>
+      <c r="Z9" s="10" t="n">
+        <v>420</v>
+      </c>
+      <c r="AA9" s="10" t="n">
+        <v>508</v>
       </c>
     </row>
     <row r="10">
@@ -1293,20 +1230,11 @@
       <c r="Y10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Z10" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB10" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC10" s="10" t="n">
-        <v>235</v>
-      </c>
-      <c r="AD10" s="10" t="n">
-        <v>235</v>
+      <c r="Z10" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="AA10" s="10" t="n">
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -1387,20 +1315,11 @@
       <c r="Y11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Z11" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC11" s="10" t="n">
-        <v>235</v>
-      </c>
-      <c r="AD11" s="10" t="n">
-        <v>235</v>
+      <c r="Z11" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="AA11" s="10" t="n">
+        <v>210</v>
       </c>
     </row>
     <row r="12">
@@ -1481,20 +1400,11 @@
       <c r="Y12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Z12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC12" s="10" t="n">
-        <v>235</v>
-      </c>
-      <c r="AD12" s="10" t="n">
-        <v>235</v>
+      <c r="Z12" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="AA12" s="10" t="n">
+        <v>210</v>
       </c>
     </row>
     <row r="13">
@@ -1575,20 +1485,11 @@
       <c r="Y13" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="Z13" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA13" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AB13" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC13" s="12" t="n">
-        <v>3525</v>
-      </c>
-      <c r="AD13" s="12" t="n">
-        <v>4005</v>
+      <c r="Z13" s="12" t="n">
+        <v>3150</v>
+      </c>
+      <c r="AA13" s="12" t="n">
+        <v>3590</v>
       </c>
     </row>
   </sheetData>
@@ -1619,7 +1520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>エリア別 供給ラインのサマリー(27ヶ月)</t>
+          <t>エリア別 供給ラインのサマリー(24ヶ月)</t>
         </is>
       </c>
     </row>
@@ -1683,16 +1584,16 @@
         <v>8</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>1410</v>
+        <v>1260</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>141000000</v>
+        <v>126000000</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>1602</v>
+        <v>1436</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>160200000</v>
+        <v>143600000</v>
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
@@ -1718,16 +1619,16 @@
         <v>3</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>470</v>
+        <v>420</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>47000000</v>
+        <v>42000000</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>566</v>
+        <v>508</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>56600000</v>
+        <v>50800000</v>
       </c>
       <c r="H5" s="16" t="inlineStr">
         <is>
@@ -1753,16 +1654,16 @@
         <v>3</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>470</v>
+        <v>420</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>47000000</v>
+        <v>42000000</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>566</v>
+        <v>508</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>56600000</v>
+        <v>50800000</v>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
@@ -1788,16 +1689,16 @@
         <v>3</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>470</v>
+        <v>420</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>47000000</v>
+        <v>42000000</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>566</v>
+        <v>508</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>56600000</v>
+        <v>50800000</v>
       </c>
       <c r="H7" s="16" t="inlineStr">
         <is>
@@ -1823,16 +1724,16 @@
         <v>1</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>235</v>
+        <v>210</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>23500000</v>
+        <v>21000000</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>235</v>
+        <v>210</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>23500000</v>
+        <v>21000000</v>
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
@@ -1858,16 +1759,16 @@
         <v>1</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>235</v>
+        <v>210</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>23500000</v>
+        <v>21000000</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>235</v>
+        <v>210</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>23500000</v>
+        <v>21000000</v>
       </c>
       <c r="H9" s="16" t="inlineStr">
         <is>
@@ -1893,16 +1794,16 @@
         <v>1</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>235</v>
+        <v>210</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>23500000</v>
+        <v>21000000</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>235</v>
+        <v>210</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>23500000</v>
+        <v>21000000</v>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
@@ -1928,16 +1829,16 @@
         <v>20</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>3525</v>
+        <v>3150</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>352500000</v>
+        <v>315000000</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>4005</v>
+        <v>3590</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>400500000</v>
+        <v>359000000</v>
       </c>
       <c r="H11" s="17" t="inlineStr"/>
       <c r="I11" s="17" t="inlineStr"/>
